--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24975" windowHeight="7635"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>对账单号</t>
   </si>
@@ -73,9 +73,15 @@
     <t>报关费用(总)</t>
   </si>
   <si>
+    <t>其他税费(总)</t>
+  </si>
+  <si>
     <t>其他费用(总)</t>
   </si>
   <si>
+    <t>对账类型</t>
+  </si>
+  <si>
     <t>对账状态</t>
   </si>
   <si>
@@ -121,7 +127,13 @@
     <t>{.declareCost}</t>
   </si>
   <si>
+    <t>{.otherTaxCost}</t>
+  </si>
+  <si>
     <t>{.otherCost}</t>
+  </si>
+  <si>
+    <t>{.reconciliationCountName}</t>
   </si>
   <si>
     <t>{.statusName}</t>
@@ -131,11 +143,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0000_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -751,8 +764,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1072,7 +1088,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -1085,13 +1101,14 @@
     <col min="10" max="10" width="19.625" customWidth="1"/>
     <col min="11" max="11" width="17.125" customWidth="1"/>
     <col min="12" max="12" width="20.125" customWidth="1"/>
-    <col min="13" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="19" customWidth="1"/>
-    <col min="15" max="15" width="17.125" customWidth="1"/>
-    <col min="16" max="16" width="16.125" customWidth="1"/>
+    <col min="13" max="13" width="17" style="1" customWidth="1"/>
+    <col min="14" max="14" width="19" style="1" customWidth="1"/>
+    <col min="15" max="16" width="17.125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="24.875" customWidth="1"/>
+    <col min="18" max="18" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1107,13 +1124,13 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -1128,67 +1145,79 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="M2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="N2" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>34</v>
+      </c>
+      <c r="R2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -121,16 +121,16 @@
     <t>{.billingWeightWithUnit}</t>
   </si>
   <si>
-    <t>{.shippingCost}</t>
-  </si>
-  <si>
-    <t>{.declareCost}</t>
-  </si>
-  <si>
-    <t>{.otherTaxCost}</t>
-  </si>
-  <si>
-    <t>{.otherCost}</t>
+    <t>{.shippingCostStr}</t>
+  </si>
+  <si>
+    <t>{.declareCostStr}</t>
+  </si>
+  <si>
+    <t>{.otherTaxCostStr}</t>
+  </si>
+  <si>
+    <t>{.otherCostStr}</t>
   </si>
   <si>
     <t>{.reconciliationCountName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
     <t>物流运费(总)</t>
   </si>
   <si>
-    <t>报关费用(总)</t>
+    <t>关税费用(总)</t>
   </si>
   <si>
     <t>其他税费(总)</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/tmsFirstMileReconciliationDetail.xlsx
@@ -43,7 +43,7 @@
     <t>物流运单号</t>
   </si>
   <si>
-    <t>货件单号</t>
+    <t>业务单号</t>
   </si>
   <si>
     <t>签收日期</t>
@@ -97,7 +97,7 @@
     <t>{.transportNo}</t>
   </si>
   <si>
-    <t>{.sourceCode}</t>
+    <t>{.businessCode}</t>
   </si>
   <si>
     <t>{.receiveDate}</t>
